--- a/data/availability/projects/la-vista-developments/patio-hills.xlsx
+++ b/data/availability/projects/la-vista-developments/patio-hills.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
